--- a/excel/Invoice_Data.xlsx
+++ b/excel/Invoice_Data.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="22">
   <si>
     <t>Company Name</t>
   </si>
@@ -77,16 +77,22 @@
     <t>Lewis Center OH</t>
   </si>
   <si>
+    <t>srinuchowdary793@gmail.com</t>
+  </si>
+  <si>
+    <t>admin@slnsolution.com</t>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
     <t>premsubhash2004@gmail.com</t>
   </si>
   <si>
-    <t>admin@slnsolution.com</t>
-  </si>
-  <si>
-    <t>April</t>
-  </si>
-  <si>
-    <t>raghuroyal779@gmail.com</t>
+    <t>subhash</t>
+  </si>
+  <si>
+    <t>nelakurthisrinu970@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -1059,8 +1065,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2"/>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="15.1333333333333" customWidth="1"/>
     <col min="2" max="2" width="16.575" customWidth="1"/>
@@ -1159,7 +1165,7 @@
       <c r="E3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G3" s="3" t="s">
@@ -1176,13 +1182,51 @@
       </c>
       <c r="K3" s="4">
         <v>12320</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4">
+        <v>120</v>
+      </c>
+      <c r="J4">
+        <v>66</v>
+      </c>
+      <c r="K4" s="4">
+        <v>10000</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="premsubhash2004@gmail.com" tooltip="mailto:premsubhash2004@gmail.com"/>
+    <hyperlink ref="F2" r:id="rId1" display="srinuchowdary793@gmail.com" tooltip="mailto:srinuchowdary793@gmail.com"/>
     <hyperlink ref="G2" r:id="rId2" display="admin@slnsolution.com"/>
     <hyperlink ref="G3" r:id="rId2" display="admin@slnsolution.com"/>
+    <hyperlink ref="F3" r:id="rId3" display="premsubhash2004@gmail.com"/>
+    <hyperlink ref="F4" r:id="rId4" display="nelakurthisrinu970@gmail.com" tooltip="mailto:nelakurthisrinu970@gmail.com"/>
+    <hyperlink ref="G4" r:id="rId2" display="admin@slnsolution.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/excel/Invoice_Data.xlsx
+++ b/excel/Invoice_Data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6800"/>
+    <workbookView windowWidth="19200" windowHeight="6200"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
   <si>
     <t>Company Name</t>
   </si>
@@ -65,6 +65,27 @@
     <t>SLN Solutions</t>
   </si>
   <si>
+    <t>prajyesh</t>
+  </si>
+  <si>
+    <t>sln</t>
+  </si>
+  <si>
+    <t xml:space="preserve">470 Olden Rd </t>
+  </si>
+  <si>
+    <t>wertyukjhgver OH</t>
+  </si>
+  <si>
+    <t>gollapalliprajyesh23@gmail.com</t>
+  </si>
+  <si>
+    <t>admin@slnsolution.com</t>
+  </si>
+  <si>
+    <t>may</t>
+  </si>
+  <si>
     <t>Srikanth Mannem</t>
   </si>
   <si>
@@ -77,16 +98,10 @@
     <t>Lewis Center OH</t>
   </si>
   <si>
-    <t>srinuchowdary793@gmail.com</t>
-  </si>
-  <si>
-    <t>admin@slnsolution.com</t>
+    <t>premsubhash2004@gmail.com</t>
   </si>
   <si>
     <t>April</t>
-  </si>
-  <si>
-    <t>premsubhash2004@gmail.com</t>
   </si>
   <si>
     <t>subhash</t>
@@ -1154,25 +1169,25 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I3">
         <v>176</v>
@@ -1189,25 +1204,25 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I4">
         <v>120</v>
@@ -1221,7 +1236,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="srinuchowdary793@gmail.com" tooltip="mailto:srinuchowdary793@gmail.com"/>
+    <hyperlink ref="F2" r:id="rId1" display="gollapalliprajyesh23@gmail.com" tooltip="mailto:gollapalliprajyesh23@gmail.com"/>
     <hyperlink ref="G2" r:id="rId2" display="admin@slnsolution.com"/>
     <hyperlink ref="G3" r:id="rId2" display="admin@slnsolution.com"/>
     <hyperlink ref="F3" r:id="rId3" display="premsubhash2004@gmail.com"/>
